--- a/Result/profitability/5514.xlsx
+++ b/Result/profitability/5514.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13125</v>
+        <v>0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>56.87625000000001</v>
+        <v>43.4675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.17375</v>
+        <v>0.11125</v>
       </c>
       <c r="N3" t="n">
-        <v>53.165</v>
+        <v>46.6</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14625</v>
+        <v>0.1475</v>
       </c>
       <c r="N4" t="n">
-        <v>55.6</v>
+        <v>44.48</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1925</v>
+        <v>0.19375</v>
       </c>
       <c r="N5" t="n">
-        <v>53.47375</v>
+        <v>39.9225</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22125</v>
+        <v>0.20625</v>
       </c>
       <c r="N6" t="n">
-        <v>49.4225</v>
+        <v>36.84875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21875</v>
+        <v>0.22375</v>
       </c>
       <c r="N7" t="n">
-        <v>46.47624999999999</v>
+        <v>33.09875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2375</v>
+        <v>0.19125</v>
       </c>
       <c r="N8" t="n">
-        <v>42.745</v>
+        <v>36.805</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-29.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-226.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.43625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.15625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-47.52</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.579804560260587</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-108.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.366914638759299</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
